--- a/samples/checked/daily/2604/incoming-b/クレーム集計260402.xlsx
+++ b/samples/checked/daily/2604/incoming-b/クレーム集計260402.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日次集計" sheetId="1" r:id="R64bae06e5a3e4ec0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日次集計" sheetId="1" r:id="R2e0c4f3bd1904453"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -264,11 +264,11 @@
   <x:cols>
     <x:col min="1" max="1" width="10.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.25" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.5" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17.25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -302,19 +302,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>skip duplicate day file</x:v>
+        <x:v>重複日次ファイルとして転記せずログ記録</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -325,19 +325,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C3" s="3" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="E3" s="3" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="F3" s="3" t="str">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>skip duplicate day file</x:v>
+        <x:v>重複日次ファイルとして転記せずログ記録</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
